--- a/Data/professors_COMPS.xlsx
+++ b/Data/professors_COMPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\kjsitfeedback\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22F1528-9964-4A89-8E39-CD22DBFA85C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB4899F-2BE9-4DAD-A680-0B410FDBDFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -270,124 +270,124 @@
     <t>Bivalkar</t>
   </si>
   <si>
-    <t>CE1</t>
-  </si>
-  <si>
-    <t>CE2</t>
-  </si>
-  <si>
-    <t>CE3</t>
-  </si>
-  <si>
-    <t>CE4</t>
-  </si>
-  <si>
-    <t>CE5</t>
-  </si>
-  <si>
-    <t>CE6</t>
-  </si>
-  <si>
-    <t>CE7</t>
-  </si>
-  <si>
-    <t>CE8</t>
-  </si>
-  <si>
-    <t>CE9</t>
-  </si>
-  <si>
-    <t>CE10</t>
-  </si>
-  <si>
-    <t>CE11</t>
-  </si>
-  <si>
-    <t>CE12</t>
-  </si>
-  <si>
-    <t>CE13</t>
-  </si>
-  <si>
-    <t>CE14</t>
-  </si>
-  <si>
-    <t>CE15</t>
-  </si>
-  <si>
-    <t>CE16</t>
-  </si>
-  <si>
-    <t>CE17</t>
-  </si>
-  <si>
-    <t>CE18</t>
-  </si>
-  <si>
-    <t>CE19</t>
-  </si>
-  <si>
-    <t>CE20</t>
-  </si>
-  <si>
-    <t>CE21</t>
-  </si>
-  <si>
-    <t>CE22</t>
-  </si>
-  <si>
-    <t>CE23</t>
-  </si>
-  <si>
-    <t>CE24</t>
-  </si>
-  <si>
-    <t>CE25</t>
-  </si>
-  <si>
-    <t>CE26</t>
-  </si>
-  <si>
-    <t>CE27</t>
-  </si>
-  <si>
-    <t>CE28</t>
-  </si>
-  <si>
-    <t>CE29</t>
-  </si>
-  <si>
-    <t>CE30</t>
-  </si>
-  <si>
-    <t>CE31</t>
-  </si>
-  <si>
-    <t>CE32</t>
-  </si>
-  <si>
-    <t>CE33</t>
-  </si>
-  <si>
-    <t>CE34</t>
-  </si>
-  <si>
-    <t>CE35</t>
-  </si>
-  <si>
-    <t>CE36</t>
-  </si>
-  <si>
-    <t>CE37</t>
-  </si>
-  <si>
-    <t>CE38</t>
-  </si>
-  <si>
-    <t>CE39</t>
-  </si>
-  <si>
-    <t>CE40</t>
+    <t>jignasha@somaiya.edu</t>
+  </si>
+  <si>
+    <t>cbhole@somaiya.edu</t>
+  </si>
+  <si>
+    <t>milind@somaiya.edu</t>
+  </si>
+  <si>
+    <t>sjadhav@somaiya.edu</t>
+  </si>
+  <si>
+    <t>nvanjari@somaiya.edu</t>
+  </si>
+  <si>
+    <t>kavitag@somaiya.edu</t>
+  </si>
+  <si>
+    <t>aarti.sahitya@somaiya.edu</t>
+  </si>
+  <si>
+    <t>shyamal@somaiya.edu</t>
+  </si>
+  <si>
+    <t>jyoti@somaiya.edu</t>
+  </si>
+  <si>
+    <t>shubhada.l@somaiya.edu</t>
+  </si>
+  <si>
+    <t>sarita.ambadekar@somaiya.edu</t>
+  </si>
+  <si>
+    <t>parag@somaiya.edu</t>
+  </si>
+  <si>
+    <t>dhanashri.kanade@somaiya.edu</t>
+  </si>
+  <si>
+    <t>priya.lande@somaiya.edu</t>
+  </si>
+  <si>
+    <t>mdesai@somaiya.edu</t>
+  </si>
+  <si>
+    <t>sayali.b@somaiya.edu</t>
+  </si>
+  <si>
+    <t>sudhashree@somaiya.edu</t>
+  </si>
+  <si>
+    <t>pyb@somaiya.edu</t>
+  </si>
+  <si>
+    <t>madhura.phadke@somaiya.edu</t>
+  </si>
+  <si>
+    <t>shreya.patankar@somaiya.edu</t>
+  </si>
+  <si>
+    <t>p.varangaonkar@somaiya.edu</t>
+  </si>
+  <si>
+    <t>abhijit.patil@somaiya.edu</t>
+  </si>
+  <si>
+    <t>nilesh.yadav@somaiya.edu</t>
+  </si>
+  <si>
+    <t>dhanashree.t@somaiya.edu</t>
+  </si>
+  <si>
+    <t>vishwayogita@somaiya.edu</t>
+  </si>
+  <si>
+    <t>vandana.salve@somaiya.edu</t>
+  </si>
+  <si>
+    <t>vaishali.bp@somaiya.edu</t>
+  </si>
+  <si>
+    <t>patil.tm@somaiya.edu</t>
+  </si>
+  <si>
+    <t>surekha.janrao@somaiya.edu</t>
+  </si>
+  <si>
+    <t>vijaya.sagvekar@somaiya.edu</t>
+  </si>
+  <si>
+    <t>hema.shukla@somaiya.edu</t>
+  </si>
+  <si>
+    <t>rina@somaiya.edu</t>
+  </si>
+  <si>
+    <t>datta.deshmukh@somaiya.edu</t>
+  </si>
+  <si>
+    <t>asmita.deshmukh@somaiya.edu</t>
+  </si>
+  <si>
+    <t>pallavi.mp@somaiya.edu</t>
+  </si>
+  <si>
+    <t>pradnya08@somaiya.edu</t>
+  </si>
+  <si>
+    <t>anand@somaiya.edu</t>
+  </si>
+  <si>
+    <t>kalpana@somaiya.edu</t>
+  </si>
+  <si>
+    <t>minal.sonkar@somaiya.edu</t>
+  </si>
+  <si>
+    <t>mbivalkar@somaiya.edu</t>
   </si>
 </sst>
 </file>

--- a/Data/professors_COMPS.xlsx
+++ b/Data/professors_COMPS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\kjsitfeedback\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soham\Documents\GitHub\kjsitfeedback\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB4899F-2BE9-4DAD-A680-0B410FDBDFE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F6E0C3-AA0D-4BDE-ACBA-4986D68259FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Professors Template" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="130">
   <si>
     <t>First Name</t>
   </si>
@@ -388,13 +388,46 @@
   </si>
   <si>
     <t>mbivalkar@somaiya.edu</t>
+  </si>
+  <si>
+    <t>Mane</t>
+  </si>
+  <si>
+    <t>pallavi.mane@somaiya.edu</t>
+  </si>
+  <si>
+    <t>BSH</t>
+  </si>
+  <si>
+    <t>Padhye</t>
+  </si>
+  <si>
+    <t>Anita</t>
+  </si>
+  <si>
+    <t>apadhye@somaiya.edu</t>
+  </si>
+  <si>
+    <t>Ghadyalji</t>
+  </si>
+  <si>
+    <t>vaishalig@somaiya.edu</t>
+  </si>
+  <si>
+    <t>rama.kulkarni@somaiya.edu</t>
+  </si>
+  <si>
+    <t>Rama</t>
+  </si>
+  <si>
+    <t>Kulkarni</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,6 +440,15 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -447,16 +489,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -757,13 +805,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -777,7 +825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -791,7 +839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -805,7 +853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -819,7 +867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -833,7 +881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -847,7 +895,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -861,7 +909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -875,7 +923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -889,7 +937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -903,7 +951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -917,7 +965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -931,7 +979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -945,7 +993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -959,7 +1007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -973,7 +1021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -987,7 +1035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1001,7 +1049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1015,7 +1063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1029,7 +1077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1043,7 +1091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1057,7 +1105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1071,7 +1119,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1085,7 +1133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1099,7 +1147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -1113,7 +1161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1127,7 +1175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1141,7 +1189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -1155,7 +1203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1169,7 +1217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1183,7 +1231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1197,7 +1245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -1211,7 +1259,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1225,7 +1273,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -1239,7 +1287,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -1253,7 +1301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1267,7 +1315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1281,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -1295,7 +1343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -1309,21 +1357,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>75</v>
       </c>
       <c r="B40" t="s">
         <v>76</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="2" t="s">
         <v>117</v>
       </c>
       <c r="D40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -1337,7 +1385,69 @@
         <v>4</v>
       </c>
     </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>123</v>
+      </c>
+      <c r="B43" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D43" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D44" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45" t="s">
+        <v>121</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C40" r:id="rId1" xr:uid="{1419C530-385C-42D2-86D5-F5AE562DC403}"/>
+    <hyperlink ref="C42" r:id="rId2" xr:uid="{A77188F2-57D6-4159-A063-DC7984338E1C}"/>
+    <hyperlink ref="C43" r:id="rId3" xr:uid="{B4671953-9C97-435B-84EA-E124CCFFA830}"/>
+    <hyperlink ref="C44" r:id="rId4" xr:uid="{2F6E5A9D-A308-40A9-B7A7-7E619E9FFBBA}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Data/professors_COMPS.xlsx
+++ b/Data/professors_COMPS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soham\Documents\GitHub\kjsitfeedback\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\kjsitfeedback\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F6E0C3-AA0D-4BDE-ACBA-4986D68259FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCAEFB3-F4FC-4AFD-AA14-E593F4E958BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Professors Template" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="133">
   <si>
     <t>First Name</t>
   </si>
@@ -421,6 +421,15 @@
   </si>
   <si>
     <t>Kulkarni</t>
+  </si>
+  <si>
+    <t>Nitin</t>
+  </si>
+  <si>
+    <t>Kenjale</t>
+  </si>
+  <si>
+    <t>nkenjale@somaiya.edu</t>
   </si>
 </sst>
 </file>
@@ -805,13 +814,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -825,7 +834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -839,7 +848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -853,7 +862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -867,7 +876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -881,7 +890,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -895,7 +904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -909,7 +918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -923,7 +932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -937,7 +946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -951,7 +960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -965,7 +974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -979,7 +988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>27</v>
       </c>
@@ -993,7 +1002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -1007,7 +1016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1021,7 +1030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -1035,7 +1044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>35</v>
       </c>
@@ -1049,7 +1058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -1063,7 +1072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1077,7 +1086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>41</v>
       </c>
@@ -1091,7 +1100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1105,7 +1114,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -1119,7 +1128,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -1133,7 +1142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>49</v>
       </c>
@@ -1147,7 +1156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>51</v>
       </c>
@@ -1161,7 +1170,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>53</v>
       </c>
@@ -1175,7 +1184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1189,7 +1198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -1203,7 +1212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
@@ -1217,7 +1226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -1231,7 +1240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>61</v>
       </c>
@@ -1245,7 +1254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -1259,7 +1268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>65</v>
       </c>
@@ -1273,7 +1282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -1301,7 +1310,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -1315,7 +1324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -1329,7 +1338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>71</v>
       </c>
@@ -1343,7 +1352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>73</v>
       </c>
@@ -1357,7 +1366,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>75</v>
       </c>
@@ -1371,7 +1380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>77</v>
       </c>
@@ -1385,7 +1394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -1399,7 +1408,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>123</v>
       </c>
@@ -1413,7 +1422,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>57</v>
       </c>
@@ -1427,7 +1436,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>128</v>
       </c>
@@ -1438,6 +1447,20 @@
         <v>127</v>
       </c>
       <c r="D45" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" t="s">
         <v>121</v>
       </c>
     </row>

--- a/Data/professors_COMPS.xlsx
+++ b/Data/professors_COMPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\kjsitfeedback\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCAEFB3-F4FC-4AFD-AA14-E593F4E958BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94059BE0-71D2-4AC3-A4AC-43F3A61987DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -817,7 +817,9 @@
   <dimension ref="A1:D46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="20" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
